--- a/benchmark/generated_files/CC-3_M_007.xlsx
+++ b/benchmark/generated_files/CC-3_M_007.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n">
-        <v>1214.06</v>
+        <v>1195.34</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n">
-        <v>1186.28</v>
+        <v>1160.8</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
       </c>
       <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n">
-        <v>1167.85</v>
+        <v>1155.73</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -556,7 +556,7 @@
       </c>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n">
-        <v>1183.84</v>
+        <v>1205.47</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -569,7 +569,7 @@
         <v>46023</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -578,7 +578,7 @@
       </c>
       <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n">
-        <v>1212.95</v>
+        <v>1152.1</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -600,7 +600,7 @@
       </c>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n">
-        <v>1200.86</v>
+        <v>1244.12</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         <v>46023</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
       </c>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n">
-        <v>1208.4</v>
+        <v>1212.95</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         <v>46023</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
       </c>
       <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n">
-        <v>1228.59</v>
+        <v>1200.86</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
       </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n">
-        <v>1187.47</v>
+        <v>1208.4</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
       </c>
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n">
-        <v>1168.67</v>
+        <v>1228.59</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n">
-        <v>1188.9</v>
+        <v>1187.47</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n">
-        <v>1219.85</v>
+        <v>1168.67</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         <v>46023</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46024</v>
+        <v>46023</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n">
-        <v>1219.8</v>
+        <v>1188.9</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n">
-        <v>1167.06</v>
+        <v>1219.85</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n">
-        <v>1217.74</v>
+        <v>1219.8</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n">
-        <v>1233.65</v>
+        <v>1167.06</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>46023</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n">
-        <v>1187.46</v>
+        <v>1217.74</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
       </c>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n">
-        <v>1172.06</v>
+        <v>1233.65</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
       </c>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n">
-        <v>1212.47</v>
+        <v>1187.46</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -903,13 +903,13 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>ACCREDITO PENSIONE INPS MESE DI GENNAIO 2026</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n">
-        <v>1238.55</v>
-      </c>
+          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>448.94</v>
+      </c>
+      <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -921,15 +921,15 @@
         <v>46024</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
+          <t>Pagam. POS - PAGAMENTO POS 130,73 EUR DEL 02.01.2026 A (ITA) BOTTEGA VERDE</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>567.66</v>
+        <v>130.73</v>
       </c>
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="inlineStr">
@@ -940,18 +940,18 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46024</v>
+        <v>46029</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46024</v>
+        <v>46030</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:217189001 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
+          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>516.1900000000001</v>
+        <v>526.36</v>
       </c>
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="inlineStr">
@@ -962,18 +962,18 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46026</v>
+        <v>46037</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46028</v>
+        <v>46037</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:216739123 BEN. ASSISTENTE FAMILIARE MOLDOVEANU</t>
+          <t>Disposizione - RIF:212816607 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>29.29</v>
+        <v>857.85</v>
       </c>
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="inlineStr">
@@ -984,18 +984,18 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46026</v>
+        <v>46044</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46026</v>
+        <v>46045</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:214976369 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
+          <t>Pagam. POS - PAGAMENTO POS 43,91 EUR DEL 22.01.2026 A (ITA) ACQUA &amp; SAPONE</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>562.17</v>
+        <v>43.91</v>
       </c>
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="inlineStr">
@@ -1006,18 +1006,18 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46034</v>
+        <v>46044</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46034</v>
+        <v>46044</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
+          <t>Disposizione - RIF:217357303 BEN. GIARDINIERE COLOMBO LUIGI</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>984.62</v>
+        <v>42.13</v>
       </c>
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="inlineStr">
@@ -1028,20 +1028,20 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46039</v>
+        <v>46044</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46039</v>
+        <v>46044</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 94,00 EUR DEL 17.01.2026 A (ITA) CENTRO DIAGNOSTICO SAN DONATO</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="E27" s="3" t="n"/>
+          <t>Bonif. v/fav. - RIF:213425984 ORD. REGIONE LOMBARDIA BONUS</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n"/>
+      <c r="E27" s="3" t="n">
+        <v>305.69</v>
+      </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1050,18 +1050,18 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46044</v>
+        <v>46046</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>46044</v>
+        <v>46046</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 129,93 EUR DEL 22.01.2026 A (ITA) CONAD SUPERSTORE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6181 SPLENDIDI E SPLENDENTI VIMODRONE</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>129.93</v>
+        <v>117.93</v>
       </c>
       <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="inlineStr">
@@ -1072,20 +1072,20 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213425984 ORD. REGIONE LOMBARDIA BONUS</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n">
-        <v>305.69</v>
-      </c>
+          <t>Disposizione - RIF:215413664 BEN. ROSSI MARCO CONTRIBUTO NONNA</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>870.9400000000001</v>
+      </c>
+      <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1094,20 +1094,20 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 27,12 EUR DEL 28.01.2026 A (ITA) MERCERIA LA BOTTEGA</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>27.12</v>
-      </c>
-      <c r="E30" s="3" t="n"/>
+          <t>Bonif. v/fav. - RIF:212938131 ORD. REGIONE LOMBARDIA BONUS</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n">
+        <v>206.05</v>
+      </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1116,19 +1116,19 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212938131 ORD. REGIONE LOMBARDIA BONUS</t>
+          <t>ACCREDITO PENSIONE INPS MESE DI FEBBRAIO 2026</t>
         </is>
       </c>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n">
-        <v>206.05</v>
+        <v>1156.58</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>46054</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n">
-        <v>1247.03</v>
+        <v>1222.46</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n">
-        <v>1211.61</v>
+        <v>1181.12</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n">
-        <v>1154.39</v>
+        <v>1219.48</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>46054</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n">
-        <v>1181.8</v>
+        <v>1237.61</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D36" s="3" t="n"/>
       <c r="E36" s="3" t="n">
-        <v>1197.38</v>
+        <v>1223.46</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="D37" s="3" t="n"/>
       <c r="E37" s="3" t="n">
-        <v>1207.14</v>
+        <v>1167.41</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="n">
-        <v>1177.3</v>
+        <v>1181.8</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D39" s="3" t="n"/>
       <c r="E39" s="3" t="n">
-        <v>1175</v>
+        <v>1197.38</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D40" s="3" t="n"/>
       <c r="E40" s="3" t="n">
-        <v>1244.58</v>
+        <v>1207.14</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="D41" s="3" t="n"/>
       <c r="E41" s="3" t="n">
-        <v>1222.25</v>
+        <v>1177.3</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D42" s="3" t="n"/>
       <c r="E42" s="3" t="n">
-        <v>1226.28</v>
+        <v>1175</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>46054</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="n">
-        <v>1213.9</v>
+        <v>1244.58</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n">
-        <v>1201.85</v>
+        <v>1222.25</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>46054</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="n">
-        <v>1208.75</v>
+        <v>1226.28</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="D46" s="3" t="n"/>
       <c r="E46" s="3" t="n">
-        <v>1241.03</v>
+        <v>1213.9</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>46054</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D47" s="3" t="n"/>
       <c r="E47" s="3" t="n">
-        <v>1191.01</v>
+        <v>1201.85</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>46054</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="D48" s="3" t="n"/>
       <c r="E48" s="3" t="n">
-        <v>1188.12</v>
+        <v>1208.75</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>46054</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="n">
-        <v>1198.48</v>
+        <v>1241.03</v>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="D50" s="3" t="n"/>
       <c r="E50" s="3" t="n">
-        <v>1151.2</v>
+        <v>1191.01</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -1556,20 +1556,20 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46061</v>
+        <v>46054</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46061</v>
+        <v>46054</v>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>986.99</v>
-      </c>
-      <c r="E51" s="3" t="n"/>
+          <t>ACCREDITO PENSIONE INPS MESE DI FEBBRAIO 2026</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n"/>
+      <c r="E51" s="3" t="n">
+        <v>1188.12</v>
+      </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1578,20 +1578,20 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46062</v>
+        <v>46054</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46062</v>
+        <v>46054</v>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 9,82 EUR DEL 09.02.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="E52" s="3" t="n"/>
+          <t>ACCREDITO PENSIONE INPS MESE DI FEBBRAIO 2026</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n">
+        <v>1198.48</v>
+      </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1600,20 +1600,20 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46063</v>
+        <v>46057</v>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213575870 ORD. AGENZIA ENTRATE RIMBORSO 730</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="3" t="n">
-        <v>150.36</v>
-      </c>
+          <t>GIROCONTO DA CC 0036218 A CC 0123456</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>957.25</v>
+      </c>
+      <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1622,20 +1622,20 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46074</v>
+        <v>46081</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46075</v>
+        <v>46082</v>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211987988 ORD. REGIONE LOMBARDIA BONUS</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="3" t="n">
-        <v>498.96</v>
-      </c>
+          <t>Pagam. POS - PAGAMENTO POS 28,75 EUR DEL 28.02.2026 A (ITA) COMPRO ORO NORD</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="E54" s="3" t="n"/>
       <c r="F54" s="3" t="inlineStr">
         <is>
           <t>EUR</t>
@@ -1644,18 +1644,18 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46077</v>
+        <v>46081</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46077</v>
+        <v>46082</v>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 35,59 EUR DEL 24.02.2026 A (ITA) PARRUCCHIERA SONIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 8,17 EUR DEL 28.02.2026 A (ITA) MAXI ZOO</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>35.59</v>
+        <v>8.17</v>
       </c>
       <c r="E55" s="3" t="n"/>
       <c r="F55" s="3" t="inlineStr">
